--- a/backend/scripts/plantilla_importacion.xlsx
+++ b/backend/scripts/plantilla_importacion.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,6 +415,12 @@
       <c r="D1" t="str">
         <v>observaciones</v>
       </c>
+      <c r="E1" t="str">
+        <v>rut</v>
+      </c>
+      <c r="F1" t="str">
+        <v>numero_registro</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -429,6 +435,12 @@
       <c r="D2" t="str">
         <v/>
       </c>
+      <c r="E2" t="str">
+        <v>12345678-9</v>
+      </c>
+      <c r="F2" t="str">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -443,6 +455,12 @@
       <c r="D3" t="str">
         <v/>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -457,17 +475,23 @@
       <c r="D4" t="str">
         <v>Licencia médica</v>
       </c>
+      <c r="E4" t="str">
+        <v>9876543-2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>045</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -480,9 +504,6 @@
         <v>responsable</v>
       </c>
       <c r="D1" t="str">
-        <v>codigo_qr</v>
-      </c>
-      <c r="E1" t="str">
         <v>activo</v>
       </c>
     </row>
@@ -496,10 +517,7 @@
       <c r="C2" t="str">
         <v>Juan Pérez</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2">
+      <c r="D2">
         <v>1</v>
       </c>
     </row>
@@ -513,10 +531,7 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3">
+      <c r="D3">
         <v>1</v>
       </c>
     </row>
@@ -530,10 +545,7 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4">
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
@@ -547,23 +559,20 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:P6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -588,16 +597,31 @@
         <v>serie</v>
       </c>
       <c r="H1" t="str">
+        <v>talla</v>
+      </c>
+      <c r="I1" t="str">
         <v>estado</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>criticidad</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>ubicacion_nombre</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
+        <v>ubicacion_detalle</v>
+      </c>
+      <c r="M1" t="str">
         <v>bombero_nombre</v>
+      </c>
+      <c r="N1" t="str">
+        <v>fecha_fabricacion</v>
+      </c>
+      <c r="O1" t="str">
+        <v>fecha_recepcion</v>
+      </c>
+      <c r="P1" t="str">
+        <v>fecha_vencimiento</v>
       </c>
     </row>
     <row r="2">
@@ -623,16 +647,31 @@
         <v>SN-001</v>
       </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>OPERATIVO</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>ALTA</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>Juan Pérez</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2022-01-15</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -658,16 +697,31 @@
         <v/>
       </c>
       <c r="H3" t="str">
+        <v>S</v>
+      </c>
+      <c r="I3" t="str">
         <v>OPERATIVO</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>ALTA</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>María González</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -693,16 +747,31 @@
         <v/>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>OPERATIVO</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>ALTA</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>Sala Trauma</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>2025-01-10</v>
+      </c>
+      <c r="P4" t="str">
+        <v>2027-01-10</v>
       </c>
     </row>
     <row r="5">
@@ -728,15 +797,30 @@
         <v>MK-123</v>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>MANTENCION</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>MEDIA</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
         <v>Bodega Principal</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v/>
       </c>
     </row>
@@ -763,21 +847,36 @@
         <v>MOT-007</v>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>OPERATIVO</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>ALTA</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>Carro 1</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
+        <v>Gaveta 2</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
   </ignoredErrors>
 </worksheet>
 </file>
